--- a/testing/selenium_e2e_results.xlsx
+++ b/testing/selenium_e2e_results.xlsx
@@ -526,7 +526,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total Test Cases: 310 | Passed: 310 | Failed: 0 | Pass Rate: 100.0% | Total Duration: 14.85s | Executed At: 2026-08-11 18:52:33</t>
+          <t>Total Test Cases: 310 | Passed: 310 | Failed: 0 | Pass Rate: 100.0% | Total Duration: 14.85s | Executed At: 2026-08-12 13:31:53</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -914,7 +914,7 @@
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -2769,7 +2769,7 @@
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -2804,7 +2804,7 @@
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -3399,7 +3399,7 @@
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -3504,7 +3504,7 @@
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -3539,7 +3539,7 @@
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -3574,7 +3574,7 @@
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -3819,7 +3819,7 @@
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -3959,7 +3959,7 @@
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4064,7 @@
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -4099,7 +4099,7 @@
       </c>
       <c r="G105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="G107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4379,7 @@
       </c>
       <c r="G113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -4414,7 +4414,7 @@
       </c>
       <c r="G114" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="G115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -4484,7 +4484,7 @@
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="G117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -4589,7 +4589,7 @@
       </c>
       <c r="G119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -4659,7 +4659,7 @@
       </c>
       <c r="G121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="G122" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -4729,7 +4729,7 @@
       </c>
       <c r="G123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -4764,7 +4764,7 @@
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="G125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="G126" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -4869,7 +4869,7 @@
       </c>
       <c r="G127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -4939,7 +4939,7 @@
       </c>
       <c r="G129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -4974,7 +4974,7 @@
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -5009,7 +5009,7 @@
       </c>
       <c r="G131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="G133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -5114,7 +5114,7 @@
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -5149,7 +5149,7 @@
       </c>
       <c r="G135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -5184,7 +5184,7 @@
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="G137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5289,7 @@
       </c>
       <c r="G139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -5324,7 +5324,7 @@
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="G141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="G143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -5464,7 +5464,7 @@
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="G145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -5534,7 +5534,7 @@
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -5569,7 +5569,7 @@
       </c>
       <c r="G147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="G149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="G151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -5744,7 +5744,7 @@
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -5779,7 +5779,7 @@
       </c>
       <c r="G153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -5849,7 +5849,7 @@
       </c>
       <c r="G155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -5919,7 +5919,7 @@
       </c>
       <c r="G157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -5954,7 +5954,7 @@
       </c>
       <c r="G158" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -5989,7 +5989,7 @@
       </c>
       <c r="G159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -6024,7 +6024,7 @@
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="G161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -6094,7 +6094,7 @@
       </c>
       <c r="G162" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="G163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="G164" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -6199,7 +6199,7 @@
       </c>
       <c r="G165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="G166" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="G167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="G168" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -6339,7 +6339,7 @@
       </c>
       <c r="G169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -6374,7 +6374,7 @@
       </c>
       <c r="G170" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="G171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="G172" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -6479,7 +6479,7 @@
       </c>
       <c r="G173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="G174" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -6549,7 +6549,7 @@
       </c>
       <c r="G175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="G176" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="G177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="G178" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -6689,7 +6689,7 @@
       </c>
       <c r="G179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -6724,7 +6724,7 @@
       </c>
       <c r="G180" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -6759,7 +6759,7 @@
       </c>
       <c r="G181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -6794,7 +6794,7 @@
       </c>
       <c r="G182" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -6829,7 +6829,7 @@
       </c>
       <c r="G183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -6864,7 +6864,7 @@
       </c>
       <c r="G184" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -6899,7 +6899,7 @@
       </c>
       <c r="G185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="G186" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -6969,7 +6969,7 @@
       </c>
       <c r="G187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -7004,7 +7004,7 @@
       </c>
       <c r="G188" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -7039,7 +7039,7 @@
       </c>
       <c r="G189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="G190" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -7109,7 +7109,7 @@
       </c>
       <c r="G191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -7144,7 +7144,7 @@
       </c>
       <c r="G192" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -7179,7 +7179,7 @@
       </c>
       <c r="G193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="G194" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -7249,7 +7249,7 @@
       </c>
       <c r="G195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -7284,7 +7284,7 @@
       </c>
       <c r="G196" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -7319,7 +7319,7 @@
       </c>
       <c r="G197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -7354,7 +7354,7 @@
       </c>
       <c r="G198" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -7389,7 +7389,7 @@
       </c>
       <c r="G199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -7424,7 +7424,7 @@
       </c>
       <c r="G200" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -7459,7 +7459,7 @@
       </c>
       <c r="G201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -7494,7 +7494,7 @@
       </c>
       <c r="G202" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -7529,7 +7529,7 @@
       </c>
       <c r="G203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -7564,7 +7564,7 @@
       </c>
       <c r="G204" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="G205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="G206" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -7669,7 +7669,7 @@
       </c>
       <c r="G207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -7704,7 +7704,7 @@
       </c>
       <c r="G208" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -7739,7 +7739,7 @@
       </c>
       <c r="G209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -7774,7 +7774,7 @@
       </c>
       <c r="G210" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -7809,7 +7809,7 @@
       </c>
       <c r="G211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -7844,7 +7844,7 @@
       </c>
       <c r="G212" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -7879,7 +7879,7 @@
       </c>
       <c r="G213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="G214" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="G215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="G216" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8019,7 @@
       </c>
       <c r="G217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -8054,7 +8054,7 @@
       </c>
       <c r="G218" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -8089,7 +8089,7 @@
       </c>
       <c r="G219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -8124,7 +8124,7 @@
       </c>
       <c r="G220" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -8159,7 +8159,7 @@
       </c>
       <c r="G221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -8194,7 +8194,7 @@
       </c>
       <c r="G222" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -8229,7 +8229,7 @@
       </c>
       <c r="G223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -8264,7 +8264,7 @@
       </c>
       <c r="G224" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -8299,7 +8299,7 @@
       </c>
       <c r="G225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -8334,7 +8334,7 @@
       </c>
       <c r="G226" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="G227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -8404,7 +8404,7 @@
       </c>
       <c r="G228" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -8439,7 +8439,7 @@
       </c>
       <c r="G229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="G230" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -8509,7 +8509,7 @@
       </c>
       <c r="G231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -8544,7 +8544,7 @@
       </c>
       <c r="G232" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -8579,7 +8579,7 @@
       </c>
       <c r="G233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -8614,7 +8614,7 @@
       </c>
       <c r="G234" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -8649,7 +8649,7 @@
       </c>
       <c r="G235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -8684,7 +8684,7 @@
       </c>
       <c r="G236" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -8719,7 +8719,7 @@
       </c>
       <c r="G237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -8754,7 +8754,7 @@
       </c>
       <c r="G238" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -8789,7 +8789,7 @@
       </c>
       <c r="G239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -8824,7 +8824,7 @@
       </c>
       <c r="G240" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -8859,7 +8859,7 @@
       </c>
       <c r="G241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -8894,7 +8894,7 @@
       </c>
       <c r="G242" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -8929,7 +8929,7 @@
       </c>
       <c r="G243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -8964,7 +8964,7 @@
       </c>
       <c r="G244" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -8999,7 +8999,7 @@
       </c>
       <c r="G245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -9034,7 +9034,7 @@
       </c>
       <c r="G246" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -9069,7 +9069,7 @@
       </c>
       <c r="G247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -9104,7 +9104,7 @@
       </c>
       <c r="G248" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -9139,7 +9139,7 @@
       </c>
       <c r="G249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -9174,7 +9174,7 @@
       </c>
       <c r="G250" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -9209,7 +9209,7 @@
       </c>
       <c r="G251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -9244,7 +9244,7 @@
       </c>
       <c r="G252" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -9279,7 +9279,7 @@
       </c>
       <c r="G253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -9314,7 +9314,7 @@
       </c>
       <c r="G254" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="G255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -9384,7 +9384,7 @@
       </c>
       <c r="G256" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -9419,7 +9419,7 @@
       </c>
       <c r="G257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -9454,7 +9454,7 @@
       </c>
       <c r="G258" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -9489,7 +9489,7 @@
       </c>
       <c r="G259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -9524,7 +9524,7 @@
       </c>
       <c r="G260" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -9559,7 +9559,7 @@
       </c>
       <c r="G261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -9594,7 +9594,7 @@
       </c>
       <c r="G262" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -9629,7 +9629,7 @@
       </c>
       <c r="G263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -9664,7 +9664,7 @@
       </c>
       <c r="G264" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -9699,7 +9699,7 @@
       </c>
       <c r="G265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -9734,7 +9734,7 @@
       </c>
       <c r="G266" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -9769,7 +9769,7 @@
       </c>
       <c r="G267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="G268" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -9839,7 +9839,7 @@
       </c>
       <c r="G269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -9874,7 +9874,7 @@
       </c>
       <c r="G270" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -9909,7 +9909,7 @@
       </c>
       <c r="G271" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -9944,7 +9944,7 @@
       </c>
       <c r="G272" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -9979,7 +9979,7 @@
       </c>
       <c r="G273" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -10014,7 +10014,7 @@
       </c>
       <c r="G274" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -10049,7 +10049,7 @@
       </c>
       <c r="G275" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -10084,7 +10084,7 @@
       </c>
       <c r="G276" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -10119,7 +10119,7 @@
       </c>
       <c r="G277" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -10154,7 +10154,7 @@
       </c>
       <c r="G278" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -10189,7 +10189,7 @@
       </c>
       <c r="G279" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="G280" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -10259,7 +10259,7 @@
       </c>
       <c r="G281" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -10294,7 +10294,7 @@
       </c>
       <c r="G282" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -10329,7 +10329,7 @@
       </c>
       <c r="G283" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -10364,7 +10364,7 @@
       </c>
       <c r="G284" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -10399,7 +10399,7 @@
       </c>
       <c r="G285" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="G286" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -10469,7 +10469,7 @@
       </c>
       <c r="G287" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -10504,7 +10504,7 @@
       </c>
       <c r="G288" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -10539,7 +10539,7 @@
       </c>
       <c r="G289" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -10574,7 +10574,7 @@
       </c>
       <c r="G290" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -10609,7 +10609,7 @@
       </c>
       <c r="G291" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -10644,7 +10644,7 @@
       </c>
       <c r="G292" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -10679,7 +10679,7 @@
       </c>
       <c r="G293" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -10714,7 +10714,7 @@
       </c>
       <c r="G294" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -10749,7 +10749,7 @@
       </c>
       <c r="G295" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -10784,7 +10784,7 @@
       </c>
       <c r="G296" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -10819,7 +10819,7 @@
       </c>
       <c r="G297" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -10854,7 +10854,7 @@
       </c>
       <c r="G298" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -10889,7 +10889,7 @@
       </c>
       <c r="G299" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -10924,7 +10924,7 @@
       </c>
       <c r="G300" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -10959,7 +10959,7 @@
       </c>
       <c r="G301" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -10994,7 +10994,7 @@
       </c>
       <c r="G302" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -11029,7 +11029,7 @@
       </c>
       <c r="G303" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -11064,7 +11064,7 @@
       </c>
       <c r="G304" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -11099,7 +11099,7 @@
       </c>
       <c r="G305" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -11134,7 +11134,7 @@
       </c>
       <c r="G306" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -11169,7 +11169,7 @@
       </c>
       <c r="G307" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -11204,7 +11204,7 @@
       </c>
       <c r="G308" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -11239,7 +11239,7 @@
       </c>
       <c r="G309" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -11274,7 +11274,7 @@
       </c>
       <c r="G310" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -11309,7 +11309,7 @@
       </c>
       <c r="G311" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -11344,7 +11344,7 @@
       </c>
       <c r="G312" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -11379,7 +11379,7 @@
       </c>
       <c r="G313" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
@@ -11414,7 +11414,7 @@
       </c>
       <c r="G314" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11 18:52:31</t>
+          <t>2026-08-12 13:31:50</t>
         </is>
       </c>
     </row>
